--- a/TEMPLATE LPM.xlsx
+++ b/TEMPLATE LPM.xlsx
@@ -278,11 +278,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="0.0"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -333,24 +333,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -361,32 +368,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -409,15 +392,55 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,38 +462,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,6 +471,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -509,7 +509,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,13 +539,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,7 +551,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,19 +587,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,49 +605,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,13 +635,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,13 +653,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,19 +689,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,15 +802,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -822,6 +813,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -850,6 +856,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -860,21 +875,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -902,154 +902,154 @@
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1073,7 +1073,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1082,13 +1082,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="6" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="6" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="7" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="7" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="36" applyAlignment="1">
@@ -1098,7 +1098,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="36" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="4" xfId="36" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="36" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1203,7 +1206,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1009650" y="7820025"/>
+          <a:off x="1009650" y="7791450"/>
           <a:ext cx="1029970" cy="890270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1255,7 +1258,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7429500"/>
+          <a:off x="0" y="7400925"/>
           <a:ext cx="1704975" cy="1695450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1293,7 +1296,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4600575" y="7772400"/>
+          <a:off x="4600575" y="7743825"/>
           <a:ext cx="1066800" cy="819150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1785,40 +1788,40 @@
     </row>
     <row r="11" ht="13.5" spans="2:18">
       <c r="B11" s="5"/>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="M11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="21" t="s">
         <v>24</v>
       </c>
       <c r="O11" s="17" t="s">
@@ -1847,66 +1850,66 @@
       <c r="O12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P12" s="20" t="s">
+      <c r="P12" s="21" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R12" s="20" t="s">
+      <c r="R12" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" ht="13.5" spans="2:18">
-      <c r="B13" s="21" t="s">
+    <row r="13" spans="2:18">
+      <c r="B13" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="21" t="s">
+      <c r="O13" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="P13" s="21" t="s">
+      <c r="P13" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="21" t="s">
+      <c r="Q13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="R13" s="21" t="s">
+      <c r="R13" s="22" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1950,17 +1953,17 @@
       <c r="N14" s="9">
         <v>0</v>
       </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="18">
+      <c r="O14" s="18">
+        <v>0</v>
+      </c>
+      <c r="P14" s="19">
         <f>O14/8*100</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="18">
+      <c r="Q14" s="18">
+        <v>0</v>
+      </c>
+      <c r="R14" s="19">
         <f>Q14/12*100</f>
         <v>0</v>
       </c>
@@ -2005,17 +2008,17 @@
       <c r="N15" s="9">
         <v>0</v>
       </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18">
+      <c r="O15" s="18">
+        <v>0</v>
+      </c>
+      <c r="P15" s="19">
         <f t="shared" ref="P15:P44" si="0">O15/8*100</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="18">
+      <c r="Q15" s="18">
+        <v>0</v>
+      </c>
+      <c r="R15" s="19">
         <f t="shared" ref="R14:R44" si="1">Q15/12*100</f>
         <v>0</v>
       </c>
@@ -2060,17 +2063,17 @@
       <c r="N16" s="9">
         <v>0</v>
       </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="18">
+      <c r="O16" s="18">
+        <v>0</v>
+      </c>
+      <c r="P16" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="18">
+      <c r="Q16" s="18">
+        <v>0</v>
+      </c>
+      <c r="R16" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2115,17 +2118,17 @@
       <c r="N17" s="9">
         <v>0</v>
       </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-      <c r="P17" s="18">
+      <c r="O17" s="18">
+        <v>0</v>
+      </c>
+      <c r="P17" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="18">
+      <c r="Q17" s="18">
+        <v>0</v>
+      </c>
+      <c r="R17" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2170,17 +2173,17 @@
       <c r="N18" s="9">
         <v>0</v>
       </c>
-      <c r="O18" s="9">
-        <v>0</v>
-      </c>
-      <c r="P18" s="18">
+      <c r="O18" s="18">
+        <v>0</v>
+      </c>
+      <c r="P18" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="18">
+      <c r="Q18" s="18">
+        <v>0</v>
+      </c>
+      <c r="R18" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2225,17 +2228,17 @@
       <c r="N19" s="9">
         <v>0</v>
       </c>
-      <c r="O19" s="9">
-        <v>0</v>
-      </c>
-      <c r="P19" s="18">
+      <c r="O19" s="18">
+        <v>0</v>
+      </c>
+      <c r="P19" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="9">
-        <v>0</v>
-      </c>
-      <c r="R19" s="18">
+      <c r="Q19" s="18">
+        <v>0</v>
+      </c>
+      <c r="R19" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2280,17 +2283,17 @@
       <c r="N20" s="9">
         <v>0</v>
       </c>
-      <c r="O20" s="9">
-        <v>0</v>
-      </c>
-      <c r="P20" s="18">
+      <c r="O20" s="18">
+        <v>0</v>
+      </c>
+      <c r="P20" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="18">
+      <c r="Q20" s="18">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2335,17 +2338,17 @@
       <c r="N21" s="9">
         <v>0</v>
       </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-      <c r="P21" s="18">
+      <c r="O21" s="18">
+        <v>0</v>
+      </c>
+      <c r="P21" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="9">
-        <v>0</v>
-      </c>
-      <c r="R21" s="18">
+      <c r="Q21" s="18">
+        <v>0</v>
+      </c>
+      <c r="R21" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2390,17 +2393,17 @@
       <c r="N22" s="9">
         <v>0</v>
       </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-      <c r="P22" s="18">
+      <c r="O22" s="18">
+        <v>0</v>
+      </c>
+      <c r="P22" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="9">
-        <v>0</v>
-      </c>
-      <c r="R22" s="18">
+      <c r="Q22" s="18">
+        <v>0</v>
+      </c>
+      <c r="R22" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2445,17 +2448,17 @@
       <c r="N23" s="9">
         <v>0</v>
       </c>
-      <c r="O23" s="9">
-        <v>0</v>
-      </c>
-      <c r="P23" s="18">
+      <c r="O23" s="18">
+        <v>0</v>
+      </c>
+      <c r="P23" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="9">
-        <v>0</v>
-      </c>
-      <c r="R23" s="18">
+      <c r="Q23" s="18">
+        <v>0</v>
+      </c>
+      <c r="R23" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2500,17 +2503,17 @@
       <c r="N24" s="9">
         <v>0</v>
       </c>
-      <c r="O24" s="9">
-        <v>0</v>
-      </c>
-      <c r="P24" s="18">
+      <c r="O24" s="18">
+        <v>0</v>
+      </c>
+      <c r="P24" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="9">
-        <v>0</v>
-      </c>
-      <c r="R24" s="18">
+      <c r="Q24" s="18">
+        <v>0</v>
+      </c>
+      <c r="R24" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2555,17 +2558,17 @@
       <c r="N25" s="9">
         <v>0</v>
       </c>
-      <c r="O25" s="9">
-        <v>0</v>
-      </c>
-      <c r="P25" s="18">
+      <c r="O25" s="18">
+        <v>0</v>
+      </c>
+      <c r="P25" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="9">
-        <v>0</v>
-      </c>
-      <c r="R25" s="18">
+      <c r="Q25" s="18">
+        <v>0</v>
+      </c>
+      <c r="R25" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2610,17 +2613,17 @@
       <c r="N26" s="9">
         <v>0</v>
       </c>
-      <c r="O26" s="9">
-        <v>0</v>
-      </c>
-      <c r="P26" s="18">
+      <c r="O26" s="18">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="9">
-        <v>0</v>
-      </c>
-      <c r="R26" s="18">
+      <c r="Q26" s="18">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2665,17 +2668,17 @@
       <c r="N27" s="9">
         <v>0</v>
       </c>
-      <c r="O27" s="9">
-        <v>0</v>
-      </c>
-      <c r="P27" s="18">
+      <c r="O27" s="18">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="9">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
+      <c r="Q27" s="18">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2720,17 +2723,17 @@
       <c r="N28" s="9">
         <v>0</v>
       </c>
-      <c r="O28" s="9">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
+      <c r="O28" s="18">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="9">
-        <v>0</v>
-      </c>
-      <c r="R28" s="18">
+      <c r="Q28" s="18">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2775,17 +2778,17 @@
       <c r="N29" s="9">
         <v>0</v>
       </c>
-      <c r="O29" s="9">
-        <v>0</v>
-      </c>
-      <c r="P29" s="18">
+      <c r="O29" s="18">
+        <v>0</v>
+      </c>
+      <c r="P29" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="9">
-        <v>0</v>
-      </c>
-      <c r="R29" s="18">
+      <c r="Q29" s="18">
+        <v>0</v>
+      </c>
+      <c r="R29" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2830,17 +2833,17 @@
       <c r="N30" s="9">
         <v>0</v>
       </c>
-      <c r="O30" s="9">
-        <v>0</v>
-      </c>
-      <c r="P30" s="18">
+      <c r="O30" s="18">
+        <v>0</v>
+      </c>
+      <c r="P30" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="9">
-        <v>0</v>
-      </c>
-      <c r="R30" s="18">
+      <c r="Q30" s="18">
+        <v>0</v>
+      </c>
+      <c r="R30" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2885,17 +2888,17 @@
       <c r="N31" s="9">
         <v>0</v>
       </c>
-      <c r="O31" s="9">
-        <v>0</v>
-      </c>
-      <c r="P31" s="18">
+      <c r="O31" s="18">
+        <v>0</v>
+      </c>
+      <c r="P31" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="9">
-        <v>0</v>
-      </c>
-      <c r="R31" s="18">
+      <c r="Q31" s="18">
+        <v>0</v>
+      </c>
+      <c r="R31" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2940,17 +2943,17 @@
       <c r="N32" s="9">
         <v>0</v>
       </c>
-      <c r="O32" s="9">
-        <v>0</v>
-      </c>
-      <c r="P32" s="18">
+      <c r="O32" s="18">
+        <v>0</v>
+      </c>
+      <c r="P32" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="9">
-        <v>0</v>
-      </c>
-      <c r="R32" s="18">
+      <c r="Q32" s="18">
+        <v>0</v>
+      </c>
+      <c r="R32" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2995,17 +2998,17 @@
       <c r="N33" s="9">
         <v>0</v>
       </c>
-      <c r="O33" s="9">
-        <v>0</v>
-      </c>
-      <c r="P33" s="18">
+      <c r="O33" s="18">
+        <v>0</v>
+      </c>
+      <c r="P33" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="9">
-        <v>0</v>
-      </c>
-      <c r="R33" s="18">
+      <c r="Q33" s="18">
+        <v>0</v>
+      </c>
+      <c r="R33" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3050,17 +3053,17 @@
       <c r="N34" s="9">
         <v>0</v>
       </c>
-      <c r="O34" s="9">
-        <v>0</v>
-      </c>
-      <c r="P34" s="18">
+      <c r="O34" s="18">
+        <v>0</v>
+      </c>
+      <c r="P34" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="9">
-        <v>0</v>
-      </c>
-      <c r="R34" s="18">
+      <c r="Q34" s="18">
+        <v>0</v>
+      </c>
+      <c r="R34" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3105,17 +3108,17 @@
       <c r="N35" s="9">
         <v>0</v>
       </c>
-      <c r="O35" s="9">
-        <v>0</v>
-      </c>
-      <c r="P35" s="18">
+      <c r="O35" s="18">
+        <v>0</v>
+      </c>
+      <c r="P35" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="9">
-        <v>0</v>
-      </c>
-      <c r="R35" s="18">
+      <c r="Q35" s="18">
+        <v>0</v>
+      </c>
+      <c r="R35" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3160,17 +3163,17 @@
       <c r="N36" s="9">
         <v>0</v>
       </c>
-      <c r="O36" s="9">
-        <v>0</v>
-      </c>
-      <c r="P36" s="18">
+      <c r="O36" s="18">
+        <v>0</v>
+      </c>
+      <c r="P36" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="9">
-        <v>0</v>
-      </c>
-      <c r="R36" s="18">
+      <c r="Q36" s="18">
+        <v>0</v>
+      </c>
+      <c r="R36" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3215,17 +3218,17 @@
       <c r="N37" s="9">
         <v>0</v>
       </c>
-      <c r="O37" s="9">
-        <v>0</v>
-      </c>
-      <c r="P37" s="18">
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="9">
-        <v>0</v>
-      </c>
-      <c r="R37" s="18">
+      <c r="Q37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3270,17 +3273,17 @@
       <c r="N38" s="9">
         <v>0</v>
       </c>
-      <c r="O38" s="9">
-        <v>0</v>
-      </c>
-      <c r="P38" s="18">
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="9">
-        <v>0</v>
-      </c>
-      <c r="R38" s="18">
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3325,17 +3328,17 @@
       <c r="N39" s="9">
         <v>0</v>
       </c>
-      <c r="O39" s="9">
-        <v>0</v>
-      </c>
-      <c r="P39" s="18">
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="9">
-        <v>0</v>
-      </c>
-      <c r="R39" s="18">
+      <c r="Q39" s="18">
+        <v>0</v>
+      </c>
+      <c r="R39" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3380,17 +3383,17 @@
       <c r="N40" s="9">
         <v>0</v>
       </c>
-      <c r="O40" s="9">
-        <v>0</v>
-      </c>
-      <c r="P40" s="18">
+      <c r="O40" s="18">
+        <v>0</v>
+      </c>
+      <c r="P40" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="9">
-        <v>0</v>
-      </c>
-      <c r="R40" s="18">
+      <c r="Q40" s="18">
+        <v>0</v>
+      </c>
+      <c r="R40" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3435,17 +3438,17 @@
       <c r="N41" s="9">
         <v>0</v>
       </c>
-      <c r="O41" s="9">
-        <v>0</v>
-      </c>
-      <c r="P41" s="18">
+      <c r="O41" s="18">
+        <v>0</v>
+      </c>
+      <c r="P41" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="9">
-        <v>0</v>
-      </c>
-      <c r="R41" s="18">
+      <c r="Q41" s="18">
+        <v>0</v>
+      </c>
+      <c r="R41" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3490,17 +3493,17 @@
       <c r="N42" s="9">
         <v>0</v>
       </c>
-      <c r="O42" s="9">
-        <v>0</v>
-      </c>
-      <c r="P42" s="18">
+      <c r="O42" s="18">
+        <v>0</v>
+      </c>
+      <c r="P42" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="9">
-        <v>0</v>
-      </c>
-      <c r="R42" s="18">
+      <c r="Q42" s="18">
+        <v>0</v>
+      </c>
+      <c r="R42" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3545,22 +3548,22 @@
       <c r="N43" s="9">
         <v>0</v>
       </c>
-      <c r="O43" s="9">
-        <v>0</v>
-      </c>
-      <c r="P43" s="18">
+      <c r="O43" s="18">
+        <v>0</v>
+      </c>
+      <c r="P43" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="9">
-        <v>0</v>
-      </c>
-      <c r="R43" s="18">
+      <c r="Q43" s="18">
+        <v>0</v>
+      </c>
+      <c r="R43" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="12.75" spans="2:18">
+    <row r="44" spans="2:18">
       <c r="B44" s="10">
         <v>31</v>
       </c>
@@ -3600,17 +3603,17 @@
       <c r="N44" s="9">
         <v>0</v>
       </c>
-      <c r="O44" s="9">
-        <v>0</v>
-      </c>
-      <c r="P44" s="18">
+      <c r="O44" s="18">
+        <v>0</v>
+      </c>
+      <c r="P44" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="9">
-        <v>0</v>
-      </c>
-      <c r="R44" s="18">
+      <c r="Q44" s="18">
+        <v>0</v>
+      </c>
+      <c r="R44" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/TEMPLATE LPM.xlsx
+++ b/TEMPLATE LPM.xlsx
@@ -277,12 +277,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="[=0]0;[=1]0;0.0"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -333,31 +334,24 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -368,8 +362,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,7 +372,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,24 +393,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -417,30 +410,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,15 +424,16 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,6 +448,37 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -509,7 +510,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,19 +564,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,97 +582,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,7 +618,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,25 +660,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,6 +803,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -813,6 +834,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -832,15 +886,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -855,197 +900,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1073,7 +1074,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">

--- a/TEMPLATE LPM.xlsx
+++ b/TEMPLATE LPM.xlsx
@@ -278,11 +278,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="181" formatCode="[=0]0;[=1]0;0.0"/>
   </numFmts>
   <fonts count="31">
@@ -341,9 +341,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -355,16 +370,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -379,7 +409,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,7 +417,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,19 +437,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -439,22 +461,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -468,17 +477,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -510,7 +510,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,19 +642,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,127 +660,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,7 +684,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,26 +803,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -841,8 +821,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -870,187 +900,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1083,13 +1083,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="6" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="7" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="36" applyAlignment="1">
@@ -1099,10 +1099,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="36" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="36" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="36" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="46" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1207,7 +1210,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1009650" y="7791450"/>
+          <a:off x="1009650" y="7800975"/>
           <a:ext cx="1029970" cy="890270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1259,7 +1262,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7400925"/>
+          <a:off x="0" y="7410450"/>
           <a:ext cx="1704975" cy="1695450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1297,7 +1300,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4600575" y="7743825"/>
+          <a:off x="4600575" y="7753350"/>
           <a:ext cx="1066800" cy="819150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1789,40 +1792,40 @@
     </row>
     <row r="11" ht="13.5" spans="2:18">
       <c r="B11" s="5"/>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="21" t="s">
+      <c r="K11" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="21" t="s">
+      <c r="M11" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="22" t="s">
         <v>24</v>
       </c>
       <c r="O11" s="17" t="s">
@@ -1851,66 +1854,66 @@
       <c r="O12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P12" s="21" t="s">
+      <c r="P12" s="22" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="R12" s="22" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="22" t="s">
+      <c r="N13" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="22" t="s">
+      <c r="O13" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="P13" s="22" t="s">
+      <c r="P13" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="22" t="s">
+      <c r="Q13" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="R13" s="22" t="s">
+      <c r="R13" s="23" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3564,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:18">
+    <row r="44" ht="12.75" spans="2:18">
       <c r="B44" s="10">
         <v>31</v>
       </c>
@@ -3675,7 +3678,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P45" s="12">
+      <c r="P45" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3683,7 +3686,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R45" s="12">
+      <c r="R45" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
